--- a/demo-import/02-35-students-grade-alef.xlsx
+++ b/demo-import/02-35-students-grade-alef.xlsx
@@ -398,1194 +398,2502 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:V36"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="14.83203125" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>שם מלא</v>
+        <v>מי</v>
       </c>
       <c r="B1" t="str">
-        <v>תעודת זהות</v>
+        <v>שם פרטי</v>
       </c>
       <c r="C1" t="str">
+        <v>משפחה</v>
+      </c>
+      <c r="D1" t="str">
+        <v>כיתה</v>
+      </c>
+      <c r="E1" t="str">
+        <v>מ.ז.</v>
+      </c>
+      <c r="F1" t="str">
+        <v>ת.ל. עברי</v>
+      </c>
+      <c r="G1" t="str">
+        <v>ת.ל. לועזי</v>
+      </c>
+      <c r="H1" t="str">
+        <v>כתובת</v>
+      </c>
+      <c r="I1" t="str">
+        <v>עיר</v>
+      </c>
+      <c r="J1" t="str">
+        <v>טל</v>
+      </c>
+      <c r="K1" t="str">
+        <v>פל אב</v>
+      </c>
+      <c r="L1" t="str">
+        <v>פל אם</v>
+      </c>
+      <c r="M1" t="str">
+        <v>פל תלמידה</v>
+      </c>
+      <c r="N1" t="str">
+        <v>תיכון</v>
+      </c>
+      <c r="O1" t="str">
+        <v>תוכנית חץ</v>
+      </c>
+      <c r="P1" t="str">
+        <v>שכבה</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>מסלול</v>
+      </c>
+      <c r="R1" t="str">
+        <v>התמחות</v>
+      </c>
+      <c r="S1" t="str">
+        <v>פסיכולוגיה</v>
+      </c>
+      <c r="T1" t="str">
+        <v>התמחות נוספת</v>
+      </c>
+      <c r="U1" t="str">
         <v>מחזור</v>
       </c>
-      <c r="D1" t="str">
-        <v>שכבה</v>
-      </c>
-      <c r="E1" t="str">
-        <v>כיתה</v>
-      </c>
-      <c r="F1" t="str">
-        <v>מסלול</v>
-      </c>
-      <c r="G1" t="str">
-        <v>התמחות</v>
-      </c>
-      <c r="H1" t="str">
-        <v>התמחות נוספת</v>
-      </c>
-      <c r="I1" t="str">
-        <v>פסיכולוגיה</v>
-      </c>
-      <c r="J1" t="str">
+      <c r="V1" t="str">
         <v>בתוקף מתאריך</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שרה כהן</v>
+        <v>א</v>
       </c>
       <c r="B2" t="str">
+        <v>שרה</v>
+      </c>
+      <c r="C2" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D2" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E2" t="str">
         <v>200000001</v>
       </c>
-      <c r="C2">
-        <v>6</v>
-      </c>
-      <c r="D2" t="str">
-        <v>א</v>
-      </c>
-      <c r="E2" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F2" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2004-01-01</v>
+      </c>
+      <c r="H2" t="str">
+        <v>רחוב הדקל 1</v>
+      </c>
+      <c r="I2" t="str">
+        <v>ירושלים</v>
+      </c>
+      <c r="J2" t="str">
+        <v>02-510101</v>
+      </c>
+      <c r="K2" t="str">
+        <v>050-71001</v>
+      </c>
+      <c r="L2" t="str">
+        <v>052-81001</v>
+      </c>
+      <c r="M2" t="str">
+        <v>058-91001</v>
+      </c>
+      <c r="N2" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O2" t="str">
+        <v>כן</v>
+      </c>
+      <c r="P2" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q2" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G2" t="str">
+      <c r="R2" t="str">
         <v>אדריכלות</v>
       </c>
-      <c r="H2" t="str">
+      <c r="S2" t="str">
+        <v>כן</v>
+      </c>
+      <c r="T2" t="str">
         <v>גרפיקה</v>
       </c>
-      <c r="I2" t="str">
-        <v>כן</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="U2">
+        <v>6</v>
+      </c>
+      <c r="V2" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מרים כהן</v>
+        <v/>
       </c>
       <c r="B3" t="str">
+        <v>מרים</v>
+      </c>
+      <c r="C3" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D3" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E3" t="str">
         <v>200000002</v>
       </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3" t="str">
-        <v>א</v>
-      </c>
-      <c r="E3" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F3" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2005-02-02</v>
+      </c>
+      <c r="H3" t="str">
+        <v>רחוב הדקל 2</v>
+      </c>
+      <c r="I3" t="str">
+        <v>בני ברק</v>
+      </c>
+      <c r="J3" t="str">
+        <v>02-510202</v>
+      </c>
+      <c r="K3" t="str">
+        <v>050-71002</v>
+      </c>
+      <c r="L3" t="str">
+        <v>052-81002</v>
+      </c>
+      <c r="M3" t="str">
+        <v>058-91002</v>
+      </c>
+      <c r="N3" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O3" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P3" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q3" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G3" t="str">
+      <c r="R3" t="str">
         <v>גרפיקה</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J3" t="str">
+      <c r="S3" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3">
+        <v>6</v>
+      </c>
+      <c r="V3" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>חנה כהן</v>
+        <v/>
       </c>
       <c r="B4" t="str">
+        <v>חנה</v>
+      </c>
+      <c r="C4" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D4" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E4" t="str">
         <v>200000003</v>
       </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="D4" t="str">
-        <v>א</v>
-      </c>
-      <c r="E4" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F4" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2006-03-03</v>
+      </c>
+      <c r="H4" t="str">
+        <v>רחוב הדקל 3</v>
+      </c>
+      <c r="I4" t="str">
+        <v>אשדוד</v>
+      </c>
+      <c r="J4" t="str">
+        <v>02-510303</v>
+      </c>
+      <c r="K4" t="str">
+        <v>050-71003</v>
+      </c>
+      <c r="L4" t="str">
+        <v>052-81003</v>
+      </c>
+      <c r="M4" t="str">
+        <v>058-91003</v>
+      </c>
+      <c r="N4" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O4" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P4" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q4" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G4" t="str">
+      <c r="R4" t="str">
         <v>הוראה מתקנת</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="S4" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4">
+        <v>6</v>
+      </c>
+      <c r="V4" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>רבקה כהן</v>
+        <v/>
       </c>
       <c r="B5" t="str">
+        <v>רבקה</v>
+      </c>
+      <c r="C5" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D5" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E5" t="str">
         <v>200000004</v>
       </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="str">
-        <v>א</v>
-      </c>
-      <c r="E5" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F5" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2007-04-04</v>
+      </c>
+      <c r="H5" t="str">
+        <v>רחוב הדקל 4</v>
+      </c>
+      <c r="I5" t="str">
+        <v>מודיעין עילית</v>
+      </c>
+      <c r="J5" t="str">
+        <v>02-510404</v>
+      </c>
+      <c r="K5" t="str">
+        <v>050-71004</v>
+      </c>
+      <c r="L5" t="str">
+        <v>052-81004</v>
+      </c>
+      <c r="M5" t="str">
+        <v>058-91004</v>
+      </c>
+      <c r="N5" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O5" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P5" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q5" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G5" t="str">
+      <c r="R5" t="str">
         <v>חינוך מיוחד</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J5" t="str">
+      <c r="S5" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5">
+        <v>6</v>
+      </c>
+      <c r="V5" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>לאה כהן</v>
+        <v/>
       </c>
       <c r="B6" t="str">
+        <v>לאה</v>
+      </c>
+      <c r="C6" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D6" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E6" t="str">
         <v>200000005</v>
       </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-      <c r="D6" t="str">
-        <v>א</v>
-      </c>
-      <c r="E6" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F6" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2004-05-05</v>
+      </c>
+      <c r="H6" t="str">
+        <v>רחוב הדקל 5</v>
+      </c>
+      <c r="I6" t="str">
+        <v>ביתר עילית</v>
+      </c>
+      <c r="J6" t="str">
+        <v>02-510505</v>
+      </c>
+      <c r="K6" t="str">
+        <v>050-71005</v>
+      </c>
+      <c r="L6" t="str">
+        <v>052-81005</v>
+      </c>
+      <c r="M6" t="str">
+        <v>058-91005</v>
+      </c>
+      <c r="N6" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O6" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P6" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q6" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G6" t="str">
+      <c r="R6" t="str">
         <v>חשבונאות</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J6" t="str">
+      <c r="S6" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T6" t="str">
+        <v/>
+      </c>
+      <c r="U6">
+        <v>6</v>
+      </c>
+      <c r="V6" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אסתר כהן</v>
+        <v>א</v>
       </c>
       <c r="B7" t="str">
+        <v>אסתר</v>
+      </c>
+      <c r="C7" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D7" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E7" t="str">
         <v>200000006</v>
       </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7" t="str">
-        <v>א</v>
-      </c>
-      <c r="E7" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F7" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2005-06-06</v>
+      </c>
+      <c r="H7" t="str">
+        <v>רחוב הדקל 6</v>
+      </c>
+      <c r="I7" t="str">
+        <v>אלעד</v>
+      </c>
+      <c r="J7" t="str">
+        <v>02-510606</v>
+      </c>
+      <c r="K7" t="str">
+        <v>050-71006</v>
+      </c>
+      <c r="L7" t="str">
+        <v>052-81006</v>
+      </c>
+      <c r="M7" t="str">
+        <v>058-91006</v>
+      </c>
+      <c r="N7" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O7" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P7" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q7" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G7" t="str">
+      <c r="R7" t="str">
         <v>תכנות</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J7" t="str">
+      <c r="S7" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T7" t="str">
+        <v/>
+      </c>
+      <c r="U7">
+        <v>6</v>
+      </c>
+      <c r="V7" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>דינה כהן</v>
+        <v/>
       </c>
       <c r="B8" t="str">
+        <v>דינה</v>
+      </c>
+      <c r="C8" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D8" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E8" t="str">
         <v>200000007</v>
       </c>
-      <c r="C8">
-        <v>6</v>
-      </c>
-      <c r="D8" t="str">
-        <v>א</v>
-      </c>
-      <c r="E8" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F8" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2006-07-07</v>
+      </c>
+      <c r="H8" t="str">
+        <v>רחוב הדקל 7</v>
+      </c>
+      <c r="I8" t="str">
+        <v>חיפה</v>
+      </c>
+      <c r="J8" t="str">
+        <v>02-510707</v>
+      </c>
+      <c r="K8" t="str">
+        <v>050-71007</v>
+      </c>
+      <c r="L8" t="str">
+        <v>052-81007</v>
+      </c>
+      <c r="M8" t="str">
+        <v>058-91007</v>
+      </c>
+      <c r="N8" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O8" t="str">
+        <v>כן</v>
+      </c>
+      <c r="P8" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q8" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G8" t="str">
+      <c r="R8" t="str">
         <v>תנך</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J8" t="str">
+      <c r="S8" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T8" t="str">
+        <v/>
+      </c>
+      <c r="U8">
+        <v>6</v>
+      </c>
+      <c r="V8" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>יעל כהן</v>
+        <v/>
       </c>
       <c r="B9" t="str">
+        <v>יעל</v>
+      </c>
+      <c r="C9" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D9" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E9" t="str">
         <v>200000008</v>
       </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9" t="str">
-        <v>א</v>
-      </c>
-      <c r="E9" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F9" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G9" t="str">
+        <v>2007-08-08</v>
+      </c>
+      <c r="H9" t="str">
+        <v>רחוב הדקל 8</v>
+      </c>
+      <c r="I9" t="str">
+        <v>ירושלים</v>
+      </c>
+      <c r="J9" t="str">
+        <v>02-510808</v>
+      </c>
+      <c r="K9" t="str">
+        <v>050-71008</v>
+      </c>
+      <c r="L9" t="str">
+        <v>052-81008</v>
+      </c>
+      <c r="M9" t="str">
+        <v>058-91008</v>
+      </c>
+      <c r="N9" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O9" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P9" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q9" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G9" t="str">
+      <c r="R9" t="str">
         <v>אדריכלות</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J9" t="str">
+      <c r="S9" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T9" t="str">
+        <v/>
+      </c>
+      <c r="U9">
+        <v>6</v>
+      </c>
+      <c r="V9" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>תמר כהן</v>
+        <v/>
       </c>
       <c r="B10" t="str">
+        <v>תמר</v>
+      </c>
+      <c r="C10" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D10" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E10" t="str">
         <v>200000009</v>
       </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10" t="str">
-        <v>א</v>
-      </c>
-      <c r="E10" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F10" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G10" t="str">
+        <v>2004-09-09</v>
+      </c>
+      <c r="H10" t="str">
+        <v>רחוב הדקל 9</v>
+      </c>
+      <c r="I10" t="str">
+        <v>בני ברק</v>
+      </c>
+      <c r="J10" t="str">
+        <v>02-510909</v>
+      </c>
+      <c r="K10" t="str">
+        <v>050-71009</v>
+      </c>
+      <c r="L10" t="str">
+        <v>052-81009</v>
+      </c>
+      <c r="M10" t="str">
+        <v>058-91009</v>
+      </c>
+      <c r="N10" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O10" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P10" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q10" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G10" t="str">
+      <c r="R10" t="str">
         <v>גרפיקה</v>
       </c>
-      <c r="H10" t="str">
+      <c r="S10" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T10" t="str">
         <v>הוראה מתקנת</v>
       </c>
-      <c r="I10" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J10" t="str">
+      <c r="U10">
+        <v>6</v>
+      </c>
+      <c r="V10" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>נעמי כהן</v>
+        <v/>
       </c>
       <c r="B11" t="str">
+        <v>נעמי</v>
+      </c>
+      <c r="C11" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D11" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E11" t="str">
         <v>200000010</v>
       </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11" t="str">
-        <v>א</v>
-      </c>
-      <c r="E11" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F11" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G11" t="str">
+        <v>2005-10-10</v>
+      </c>
+      <c r="H11" t="str">
+        <v>רחוב הדקל 10</v>
+      </c>
+      <c r="I11" t="str">
+        <v>אשדוד</v>
+      </c>
+      <c r="J11" t="str">
+        <v>02-511010</v>
+      </c>
+      <c r="K11" t="str">
+        <v>050-71010</v>
+      </c>
+      <c r="L11" t="str">
+        <v>052-81010</v>
+      </c>
+      <c r="M11" t="str">
+        <v>058-91010</v>
+      </c>
+      <c r="N11" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O11" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P11" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q11" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G11" t="str">
+      <c r="R11" t="str">
         <v>הוראה מתקנת</v>
       </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J11" t="str">
+      <c r="S11" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T11" t="str">
+        <v/>
+      </c>
+      <c r="U11">
+        <v>6</v>
+      </c>
+      <c r="V11" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ברכה כהן</v>
+        <v>א</v>
       </c>
       <c r="B12" t="str">
+        <v>ברכה</v>
+      </c>
+      <c r="C12" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D12" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E12" t="str">
         <v>200000011</v>
       </c>
-      <c r="C12">
-        <v>6</v>
-      </c>
-      <c r="D12" t="str">
-        <v>א</v>
-      </c>
-      <c r="E12" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F12" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G12" t="str">
+        <v>2006-11-11</v>
+      </c>
+      <c r="H12" t="str">
+        <v>רחוב הדקל 11</v>
+      </c>
+      <c r="I12" t="str">
+        <v>מודיעין עילית</v>
+      </c>
+      <c r="J12" t="str">
+        <v>02-511111</v>
+      </c>
+      <c r="K12" t="str">
+        <v>050-71011</v>
+      </c>
+      <c r="L12" t="str">
+        <v>052-81011</v>
+      </c>
+      <c r="M12" t="str">
+        <v>058-91011</v>
+      </c>
+      <c r="N12" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O12" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P12" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q12" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G12" t="str">
+      <c r="R12" t="str">
         <v>חינוך מיוחד</v>
       </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J12" t="str">
+      <c r="S12" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T12" t="str">
+        <v/>
+      </c>
+      <c r="U12">
+        <v>6</v>
+      </c>
+      <c r="V12" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>פייגי כהן</v>
+        <v/>
       </c>
       <c r="B13" t="str">
+        <v>פייגי</v>
+      </c>
+      <c r="C13" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D13" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E13" t="str">
         <v>200000012</v>
       </c>
-      <c r="C13">
-        <v>6</v>
-      </c>
-      <c r="D13" t="str">
-        <v>א</v>
-      </c>
-      <c r="E13" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F13" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G13" t="str">
+        <v>2007-12-12</v>
+      </c>
+      <c r="H13" t="str">
+        <v>רחוב הדקל 12</v>
+      </c>
+      <c r="I13" t="str">
+        <v>ביתר עילית</v>
+      </c>
+      <c r="J13" t="str">
+        <v>02-511212</v>
+      </c>
+      <c r="K13" t="str">
+        <v>050-71012</v>
+      </c>
+      <c r="L13" t="str">
+        <v>052-81012</v>
+      </c>
+      <c r="M13" t="str">
+        <v>058-91012</v>
+      </c>
+      <c r="N13" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O13" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P13" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q13" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G13" t="str">
+      <c r="R13" t="str">
         <v>חשבונאות</v>
       </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J13" t="str">
+      <c r="S13" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T13" t="str">
+        <v/>
+      </c>
+      <c r="U13">
+        <v>6</v>
+      </c>
+      <c r="V13" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>מלכה כהן</v>
+        <v/>
       </c>
       <c r="B14" t="str">
+        <v>מלכה</v>
+      </c>
+      <c r="C14" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D14" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E14" t="str">
         <v>200000013</v>
       </c>
-      <c r="C14">
-        <v>6</v>
-      </c>
-      <c r="D14" t="str">
-        <v>א</v>
-      </c>
-      <c r="E14" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F14" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G14" t="str">
+        <v>2004-01-13</v>
+      </c>
+      <c r="H14" t="str">
+        <v>רחוב הדקל 13</v>
+      </c>
+      <c r="I14" t="str">
+        <v>אלעד</v>
+      </c>
+      <c r="J14" t="str">
+        <v>02-511313</v>
+      </c>
+      <c r="K14" t="str">
+        <v>050-71013</v>
+      </c>
+      <c r="L14" t="str">
+        <v>052-81013</v>
+      </c>
+      <c r="M14" t="str">
+        <v>058-91013</v>
+      </c>
+      <c r="N14" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O14" t="str">
+        <v>כן</v>
+      </c>
+      <c r="P14" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q14" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G14" t="str">
+      <c r="R14" t="str">
         <v>תכנות</v>
       </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
+      <c r="S14" t="str">
         <v>כן</v>
       </c>
-      <c r="J14" t="str">
+      <c r="T14" t="str">
+        <v/>
+      </c>
+      <c r="U14">
+        <v>6</v>
+      </c>
+      <c r="V14" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>רותי כהן</v>
+        <v/>
       </c>
       <c r="B15" t="str">
+        <v>רותי</v>
+      </c>
+      <c r="C15" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D15" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E15" t="str">
         <v>200000014</v>
       </c>
-      <c r="C15">
-        <v>6</v>
-      </c>
-      <c r="D15" t="str">
-        <v>א</v>
-      </c>
-      <c r="E15" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F15" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G15" t="str">
+        <v>2005-02-14</v>
+      </c>
+      <c r="H15" t="str">
+        <v>רחוב הדקל 14</v>
+      </c>
+      <c r="I15" t="str">
+        <v>חיפה</v>
+      </c>
+      <c r="J15" t="str">
+        <v>02-511414</v>
+      </c>
+      <c r="K15" t="str">
+        <v>050-71014</v>
+      </c>
+      <c r="L15" t="str">
+        <v>052-81014</v>
+      </c>
+      <c r="M15" t="str">
+        <v>058-91014</v>
+      </c>
+      <c r="N15" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O15" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P15" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q15" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G15" t="str">
+      <c r="R15" t="str">
         <v>תנך</v>
       </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J15" t="str">
+      <c r="S15" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T15" t="str">
+        <v/>
+      </c>
+      <c r="U15">
+        <v>6</v>
+      </c>
+      <c r="V15" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>גיטי כהן</v>
+        <v/>
       </c>
       <c r="B16" t="str">
+        <v>גיטי</v>
+      </c>
+      <c r="C16" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D16" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E16" t="str">
         <v>200000015</v>
       </c>
-      <c r="C16">
-        <v>6</v>
-      </c>
-      <c r="D16" t="str">
-        <v>א</v>
-      </c>
-      <c r="E16" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F16" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2006-03-15</v>
+      </c>
+      <c r="H16" t="str">
+        <v>רחוב הדקל 15</v>
+      </c>
+      <c r="I16" t="str">
+        <v>ירושלים</v>
+      </c>
+      <c r="J16" t="str">
+        <v>02-511515</v>
+      </c>
+      <c r="K16" t="str">
+        <v>050-71015</v>
+      </c>
+      <c r="L16" t="str">
+        <v>052-81015</v>
+      </c>
+      <c r="M16" t="str">
+        <v>058-91015</v>
+      </c>
+      <c r="N16" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O16" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P16" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q16" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G16" t="str">
+      <c r="R16" t="str">
         <v>אדריכלות</v>
       </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J16" t="str">
+      <c r="S16" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T16" t="str">
+        <v/>
+      </c>
+      <c r="U16">
+        <v>6</v>
+      </c>
+      <c r="V16" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ציפורה כהן</v>
+        <v>א</v>
       </c>
       <c r="B17" t="str">
+        <v>ציפורה</v>
+      </c>
+      <c r="C17" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D17" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E17" t="str">
         <v>200000016</v>
       </c>
-      <c r="C17">
-        <v>6</v>
-      </c>
-      <c r="D17" t="str">
-        <v>א</v>
-      </c>
-      <c r="E17" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F17" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G17" t="str">
+        <v>2007-04-16</v>
+      </c>
+      <c r="H17" t="str">
+        <v>רחוב הדקל 16</v>
+      </c>
+      <c r="I17" t="str">
+        <v>בני ברק</v>
+      </c>
+      <c r="J17" t="str">
+        <v>02-511616</v>
+      </c>
+      <c r="K17" t="str">
+        <v>050-71016</v>
+      </c>
+      <c r="L17" t="str">
+        <v>052-81016</v>
+      </c>
+      <c r="M17" t="str">
+        <v>058-91016</v>
+      </c>
+      <c r="N17" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O17" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P17" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q17" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G17" t="str">
+      <c r="R17" t="str">
         <v>גרפיקה</v>
       </c>
-      <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J17" t="str">
+      <c r="S17" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T17" t="str">
+        <v/>
+      </c>
+      <c r="U17">
+        <v>6</v>
+      </c>
+      <c r="V17" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>גולדה כהן</v>
+        <v/>
       </c>
       <c r="B18" t="str">
+        <v>גולדה</v>
+      </c>
+      <c r="C18" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D18" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E18" t="str">
         <v>200000017</v>
       </c>
-      <c r="C18">
-        <v>6</v>
-      </c>
-      <c r="D18" t="str">
-        <v>א</v>
-      </c>
-      <c r="E18" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F18" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G18" t="str">
+        <v>2004-05-17</v>
+      </c>
+      <c r="H18" t="str">
+        <v>רחוב הדקל 17</v>
+      </c>
+      <c r="I18" t="str">
+        <v>אשדוד</v>
+      </c>
+      <c r="J18" t="str">
+        <v>02-511717</v>
+      </c>
+      <c r="K18" t="str">
+        <v>050-71017</v>
+      </c>
+      <c r="L18" t="str">
+        <v>052-81017</v>
+      </c>
+      <c r="M18" t="str">
+        <v>058-91017</v>
+      </c>
+      <c r="N18" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O18" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P18" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q18" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G18" t="str">
+      <c r="R18" t="str">
         <v>הוראה מתקנת</v>
       </c>
-      <c r="H18" t="str">
+      <c r="S18" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T18" t="str">
         <v>חינוך מיוחד</v>
       </c>
-      <c r="I18" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J18" t="str">
+      <c r="U18">
+        <v>6</v>
+      </c>
+      <c r="V18" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>בתיה כהן</v>
+        <v/>
       </c>
       <c r="B19" t="str">
+        <v>בתיה</v>
+      </c>
+      <c r="C19" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D19" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E19" t="str">
         <v>200000018</v>
       </c>
-      <c r="C19">
-        <v>6</v>
-      </c>
-      <c r="D19" t="str">
-        <v>א</v>
-      </c>
-      <c r="E19" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F19" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G19" t="str">
+        <v>2005-06-18</v>
+      </c>
+      <c r="H19" t="str">
+        <v>רחוב הדקל 18</v>
+      </c>
+      <c r="I19" t="str">
+        <v>מודיעין עילית</v>
+      </c>
+      <c r="J19" t="str">
+        <v>02-511818</v>
+      </c>
+      <c r="K19" t="str">
+        <v>050-71018</v>
+      </c>
+      <c r="L19" t="str">
+        <v>052-81018</v>
+      </c>
+      <c r="M19" t="str">
+        <v>058-91018</v>
+      </c>
+      <c r="N19" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O19" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P19" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q19" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G19" t="str">
+      <c r="R19" t="str">
         <v>חינוך מיוחד</v>
       </c>
-      <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J19" t="str">
+      <c r="S19" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T19" t="str">
+        <v/>
+      </c>
+      <c r="U19">
+        <v>6</v>
+      </c>
+      <c r="V19" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>שולמית כהן</v>
+        <v/>
       </c>
       <c r="B20" t="str">
+        <v>שולמית</v>
+      </c>
+      <c r="C20" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D20" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E20" t="str">
         <v>200000019</v>
       </c>
-      <c r="C20">
-        <v>6</v>
-      </c>
-      <c r="D20" t="str">
-        <v>א</v>
-      </c>
-      <c r="E20" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F20" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G20" t="str">
+        <v>2006-07-19</v>
+      </c>
+      <c r="H20" t="str">
+        <v>רחוב הדקל 19</v>
+      </c>
+      <c r="I20" t="str">
+        <v>ביתר עילית</v>
+      </c>
+      <c r="J20" t="str">
+        <v>02-511919</v>
+      </c>
+      <c r="K20" t="str">
+        <v>050-71019</v>
+      </c>
+      <c r="L20" t="str">
+        <v>052-81019</v>
+      </c>
+      <c r="M20" t="str">
+        <v>058-91019</v>
+      </c>
+      <c r="N20" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O20" t="str">
+        <v>כן</v>
+      </c>
+      <c r="P20" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q20" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G20" t="str">
+      <c r="R20" t="str">
         <v>חשבונאות</v>
       </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J20" t="str">
+      <c r="S20" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T20" t="str">
+        <v/>
+      </c>
+      <c r="U20">
+        <v>6</v>
+      </c>
+      <c r="V20" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>הדסה כהן</v>
+        <v/>
       </c>
       <c r="B21" t="str">
+        <v>הדסה</v>
+      </c>
+      <c r="C21" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D21" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E21" t="str">
         <v>200000020</v>
       </c>
-      <c r="C21">
-        <v>6</v>
-      </c>
-      <c r="D21" t="str">
-        <v>א</v>
-      </c>
-      <c r="E21" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F21" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G21" t="str">
+        <v>2007-08-20</v>
+      </c>
+      <c r="H21" t="str">
+        <v>רחוב הדקל 20</v>
+      </c>
+      <c r="I21" t="str">
+        <v>אלעד</v>
+      </c>
+      <c r="J21" t="str">
+        <v>02-512020</v>
+      </c>
+      <c r="K21" t="str">
+        <v>050-71020</v>
+      </c>
+      <c r="L21" t="str">
+        <v>052-81020</v>
+      </c>
+      <c r="M21" t="str">
+        <v>058-91020</v>
+      </c>
+      <c r="N21" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O21" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P21" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q21" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G21" t="str">
+      <c r="R21" t="str">
         <v>תכנות</v>
       </c>
-      <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J21" t="str">
+      <c r="S21" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T21" t="str">
+        <v/>
+      </c>
+      <c r="U21">
+        <v>6</v>
+      </c>
+      <c r="V21" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אסנת כהן</v>
+        <v>א</v>
       </c>
       <c r="B22" t="str">
+        <v>אסנת</v>
+      </c>
+      <c r="C22" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D22" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E22" t="str">
         <v>200000021</v>
       </c>
-      <c r="C22">
-        <v>6</v>
-      </c>
-      <c r="D22" t="str">
-        <v>א</v>
-      </c>
-      <c r="E22" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F22" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2004-09-21</v>
+      </c>
+      <c r="H22" t="str">
+        <v>רחוב הדקל 21</v>
+      </c>
+      <c r="I22" t="str">
+        <v>חיפה</v>
+      </c>
+      <c r="J22" t="str">
+        <v>02-512121</v>
+      </c>
+      <c r="K22" t="str">
+        <v>050-71021</v>
+      </c>
+      <c r="L22" t="str">
+        <v>052-81021</v>
+      </c>
+      <c r="M22" t="str">
+        <v>058-91021</v>
+      </c>
+      <c r="N22" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O22" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P22" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q22" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G22" t="str">
+      <c r="R22" t="str">
         <v>תנך</v>
       </c>
-      <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J22" t="str">
+      <c r="S22" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T22" t="str">
+        <v/>
+      </c>
+      <c r="U22">
+        <v>6</v>
+      </c>
+      <c r="V22" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>יהודית כהן</v>
+        <v/>
       </c>
       <c r="B23" t="str">
+        <v>יהודית</v>
+      </c>
+      <c r="C23" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D23" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E23" t="str">
         <v>200000022</v>
       </c>
-      <c r="C23">
-        <v>6</v>
-      </c>
-      <c r="D23" t="str">
-        <v>א</v>
-      </c>
-      <c r="E23" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F23" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G23" t="str">
+        <v>2005-10-22</v>
+      </c>
+      <c r="H23" t="str">
+        <v>רחוב הדקל 22</v>
+      </c>
+      <c r="I23" t="str">
+        <v>ירושלים</v>
+      </c>
+      <c r="J23" t="str">
+        <v>02-512222</v>
+      </c>
+      <c r="K23" t="str">
+        <v>050-71022</v>
+      </c>
+      <c r="L23" t="str">
+        <v>052-81022</v>
+      </c>
+      <c r="M23" t="str">
+        <v>058-91022</v>
+      </c>
+      <c r="N23" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O23" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P23" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q23" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G23" t="str">
+      <c r="R23" t="str">
         <v>אדריכלות</v>
       </c>
-      <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J23" t="str">
+      <c r="S23" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T23" t="str">
+        <v/>
+      </c>
+      <c r="U23">
+        <v>6</v>
+      </c>
+      <c r="V23" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>פנינה כהן</v>
+        <v/>
       </c>
       <c r="B24" t="str">
+        <v>פנינה</v>
+      </c>
+      <c r="C24" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D24" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E24" t="str">
         <v>200000023</v>
       </c>
-      <c r="C24">
-        <v>6</v>
-      </c>
-      <c r="D24" t="str">
-        <v>א</v>
-      </c>
-      <c r="E24" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F24" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G24" t="str">
+        <v>2006-11-23</v>
+      </c>
+      <c r="H24" t="str">
+        <v>רחוב הדקל 23</v>
+      </c>
+      <c r="I24" t="str">
+        <v>בני ברק</v>
+      </c>
+      <c r="J24" t="str">
+        <v>02-512323</v>
+      </c>
+      <c r="K24" t="str">
+        <v>050-71023</v>
+      </c>
+      <c r="L24" t="str">
+        <v>052-81023</v>
+      </c>
+      <c r="M24" t="str">
+        <v>058-91023</v>
+      </c>
+      <c r="N24" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O24" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P24" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q24" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G24" t="str">
+      <c r="R24" t="str">
         <v>גרפיקה</v>
       </c>
-      <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J24" t="str">
+      <c r="S24" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T24" t="str">
+        <v/>
+      </c>
+      <c r="U24">
+        <v>6</v>
+      </c>
+      <c r="V24" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>רחל לוי</v>
+        <v/>
       </c>
       <c r="B25" t="str">
+        <v>רייזי</v>
+      </c>
+      <c r="C25" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D25" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E25" t="str">
         <v>200000024</v>
       </c>
-      <c r="C25">
-        <v>6</v>
-      </c>
-      <c r="D25" t="str">
-        <v>א</v>
-      </c>
-      <c r="E25" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F25" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G25" t="str">
+        <v>2007-12-24</v>
+      </c>
+      <c r="H25" t="str">
+        <v>רחוב הדקל 24</v>
+      </c>
+      <c r="I25" t="str">
+        <v>אשדוד</v>
+      </c>
+      <c r="J25" t="str">
+        <v>02-512424</v>
+      </c>
+      <c r="K25" t="str">
+        <v>050-71024</v>
+      </c>
+      <c r="L25" t="str">
+        <v>052-81024</v>
+      </c>
+      <c r="M25" t="str">
+        <v>058-91024</v>
+      </c>
+      <c r="N25" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O25" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P25" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q25" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G25" t="str">
+      <c r="R25" t="str">
         <v>הוראה מתקנת</v>
       </c>
-      <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J25" t="str">
+      <c r="S25" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T25" t="str">
+        <v/>
+      </c>
+      <c r="U25">
+        <v>6</v>
+      </c>
+      <c r="V25" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>שרה לוי</v>
+        <v/>
       </c>
       <c r="B26" t="str">
+        <v>בילא</v>
+      </c>
+      <c r="C26" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D26" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E26" t="str">
         <v>200000025</v>
       </c>
-      <c r="C26">
-        <v>6</v>
-      </c>
-      <c r="D26" t="str">
-        <v>א</v>
-      </c>
-      <c r="E26" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F26" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G26" t="str">
+        <v>2004-01-25</v>
+      </c>
+      <c r="H26" t="str">
+        <v>רחוב הדקל 25</v>
+      </c>
+      <c r="I26" t="str">
+        <v>מודיעין עילית</v>
+      </c>
+      <c r="J26" t="str">
+        <v>02-512525</v>
+      </c>
+      <c r="K26" t="str">
+        <v>050-71025</v>
+      </c>
+      <c r="L26" t="str">
+        <v>052-81025</v>
+      </c>
+      <c r="M26" t="str">
+        <v>058-91025</v>
+      </c>
+      <c r="N26" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O26" t="str">
+        <v>כן</v>
+      </c>
+      <c r="P26" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q26" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G26" t="str">
+      <c r="R26" t="str">
         <v>חינוך מיוחד</v>
       </c>
-      <c r="H26" t="str">
+      <c r="S26" t="str">
+        <v>כן</v>
+      </c>
+      <c r="T26" t="str">
         <v>חשבונאות</v>
       </c>
-      <c r="I26" t="str">
-        <v>כן</v>
-      </c>
-      <c r="J26" t="str">
+      <c r="U26">
+        <v>6</v>
+      </c>
+      <c r="V26" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>מרים לוי</v>
+        <v>א</v>
       </c>
       <c r="B27" t="str">
+        <v>שיינדל</v>
+      </c>
+      <c r="C27" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D27" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E27" t="str">
         <v>200000026</v>
       </c>
-      <c r="C27">
-        <v>6</v>
-      </c>
-      <c r="D27" t="str">
-        <v>א</v>
-      </c>
-      <c r="E27" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F27" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G27" t="str">
+        <v>2005-02-26</v>
+      </c>
+      <c r="H27" t="str">
+        <v>רחוב הדקל 26</v>
+      </c>
+      <c r="I27" t="str">
+        <v>ביתר עילית</v>
+      </c>
+      <c r="J27" t="str">
+        <v>02-512626</v>
+      </c>
+      <c r="K27" t="str">
+        <v>050-71026</v>
+      </c>
+      <c r="L27" t="str">
+        <v>052-81026</v>
+      </c>
+      <c r="M27" t="str">
+        <v>058-91026</v>
+      </c>
+      <c r="N27" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O27" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P27" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q27" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G27" t="str">
+      <c r="R27" t="str">
         <v>חשבונאות</v>
       </c>
-      <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J27" t="str">
+      <c r="S27" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T27" t="str">
+        <v/>
+      </c>
+      <c r="U27">
+        <v>6</v>
+      </c>
+      <c r="V27" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>חנה לוי</v>
+        <v/>
       </c>
       <c r="B28" t="str">
+        <v>פרידה</v>
+      </c>
+      <c r="C28" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D28" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E28" t="str">
         <v>200000027</v>
       </c>
-      <c r="C28">
-        <v>6</v>
-      </c>
-      <c r="D28" t="str">
-        <v>א</v>
-      </c>
-      <c r="E28" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F28" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2006-03-27</v>
+      </c>
+      <c r="H28" t="str">
+        <v>רחוב הדקל 27</v>
+      </c>
+      <c r="I28" t="str">
+        <v>אלעד</v>
+      </c>
+      <c r="J28" t="str">
+        <v>02-512727</v>
+      </c>
+      <c r="K28" t="str">
+        <v>050-71027</v>
+      </c>
+      <c r="L28" t="str">
+        <v>052-81027</v>
+      </c>
+      <c r="M28" t="str">
+        <v>058-91027</v>
+      </c>
+      <c r="N28" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O28" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P28" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q28" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G28" t="str">
+      <c r="R28" t="str">
         <v>תכנות</v>
       </c>
-      <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J28" t="str">
+      <c r="S28" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T28" t="str">
+        <v/>
+      </c>
+      <c r="U28">
+        <v>6</v>
+      </c>
+      <c r="V28" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>רבקה לוי</v>
+        <v/>
       </c>
       <c r="B29" t="str">
+        <v>חוה</v>
+      </c>
+      <c r="C29" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D29" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E29" t="str">
         <v>200000028</v>
       </c>
-      <c r="C29">
-        <v>6</v>
-      </c>
-      <c r="D29" t="str">
-        <v>א</v>
-      </c>
-      <c r="E29" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F29" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G29" t="str">
+        <v>2007-04-01</v>
+      </c>
+      <c r="H29" t="str">
+        <v>רחוב הדקל 28</v>
+      </c>
+      <c r="I29" t="str">
+        <v>חיפה</v>
+      </c>
+      <c r="J29" t="str">
+        <v>02-512828</v>
+      </c>
+      <c r="K29" t="str">
+        <v>050-71028</v>
+      </c>
+      <c r="L29" t="str">
+        <v>052-81028</v>
+      </c>
+      <c r="M29" t="str">
+        <v>058-91028</v>
+      </c>
+      <c r="N29" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O29" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P29" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q29" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G29" t="str">
+      <c r="R29" t="str">
         <v>תנך</v>
       </c>
-      <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J29" t="str">
+      <c r="S29" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T29" t="str">
+        <v/>
+      </c>
+      <c r="U29">
+        <v>6</v>
+      </c>
+      <c r="V29" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>לאה לוי</v>
+        <v/>
       </c>
       <c r="B30" t="str">
+        <v>מיכל</v>
+      </c>
+      <c r="C30" t="str">
+        <v>כהן</v>
+      </c>
+      <c r="D30" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E30" t="str">
         <v>200000029</v>
       </c>
-      <c r="C30">
-        <v>6</v>
-      </c>
-      <c r="D30" t="str">
-        <v>א</v>
-      </c>
-      <c r="E30" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F30" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G30" t="str">
+        <v>2004-05-02</v>
+      </c>
+      <c r="H30" t="str">
+        <v>רחוב הדקל 29</v>
+      </c>
+      <c r="I30" t="str">
+        <v>ירושלים</v>
+      </c>
+      <c r="J30" t="str">
+        <v>02-512929</v>
+      </c>
+      <c r="K30" t="str">
+        <v>050-71029</v>
+      </c>
+      <c r="L30" t="str">
+        <v>052-81029</v>
+      </c>
+      <c r="M30" t="str">
+        <v>058-91029</v>
+      </c>
+      <c r="N30" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O30" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P30" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q30" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G30" t="str">
+      <c r="R30" t="str">
         <v>אדריכלות</v>
       </c>
-      <c r="H30" t="str">
-        <v/>
-      </c>
-      <c r="I30" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J30" t="str">
+      <c r="S30" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T30" t="str">
+        <v/>
+      </c>
+      <c r="U30">
+        <v>6</v>
+      </c>
+      <c r="V30" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>אסתר לוי</v>
+        <v/>
       </c>
       <c r="B31" t="str">
+        <v>רחל</v>
+      </c>
+      <c r="C31" t="str">
+        <v>לוי</v>
+      </c>
+      <c r="D31" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E31" t="str">
         <v>200000030</v>
       </c>
-      <c r="C31">
-        <v>6</v>
-      </c>
-      <c r="D31" t="str">
-        <v>א</v>
-      </c>
-      <c r="E31" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F31" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G31" t="str">
+        <v>2005-06-03</v>
+      </c>
+      <c r="H31" t="str">
+        <v>רחוב הדקל 30</v>
+      </c>
+      <c r="I31" t="str">
+        <v>בני ברק</v>
+      </c>
+      <c r="J31" t="str">
+        <v>02-513030</v>
+      </c>
+      <c r="K31" t="str">
+        <v>050-71030</v>
+      </c>
+      <c r="L31" t="str">
+        <v>052-81030</v>
+      </c>
+      <c r="M31" t="str">
+        <v>058-91030</v>
+      </c>
+      <c r="N31" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O31" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P31" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q31" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G31" t="str">
+      <c r="R31" t="str">
         <v>גרפיקה</v>
       </c>
-      <c r="H31" t="str">
-        <v/>
-      </c>
-      <c r="I31" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J31" t="str">
+      <c r="S31" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T31" t="str">
+        <v/>
+      </c>
+      <c r="U31">
+        <v>6</v>
+      </c>
+      <c r="V31" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>דינה לוי</v>
+        <v>א</v>
       </c>
       <c r="B32" t="str">
+        <v>שרה</v>
+      </c>
+      <c r="C32" t="str">
+        <v>לוי</v>
+      </c>
+      <c r="D32" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E32" t="str">
         <v>200000031</v>
       </c>
-      <c r="C32">
-        <v>6</v>
-      </c>
-      <c r="D32" t="str">
-        <v>א</v>
-      </c>
-      <c r="E32" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F32" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G32" t="str">
+        <v>2006-07-04</v>
+      </c>
+      <c r="H32" t="str">
+        <v>רחוב הדקל 31</v>
+      </c>
+      <c r="I32" t="str">
+        <v>אשדוד</v>
+      </c>
+      <c r="J32" t="str">
+        <v>02-513131</v>
+      </c>
+      <c r="K32" t="str">
+        <v>050-71031</v>
+      </c>
+      <c r="L32" t="str">
+        <v>052-81031</v>
+      </c>
+      <c r="M32" t="str">
+        <v>058-91031</v>
+      </c>
+      <c r="N32" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O32" t="str">
+        <v>כן</v>
+      </c>
+      <c r="P32" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q32" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G32" t="str">
+      <c r="R32" t="str">
         <v>הוראה מתקנת</v>
       </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J32" t="str">
+      <c r="S32" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T32" t="str">
+        <v/>
+      </c>
+      <c r="U32">
+        <v>6</v>
+      </c>
+      <c r="V32" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>יעל לוי</v>
+        <v/>
       </c>
       <c r="B33" t="str">
+        <v>מרים</v>
+      </c>
+      <c r="C33" t="str">
+        <v>לוי</v>
+      </c>
+      <c r="D33" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E33" t="str">
         <v>200000032</v>
       </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-      <c r="D33" t="str">
-        <v>א</v>
-      </c>
-      <c r="E33" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F33" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G33" t="str">
+        <v>2007-08-05</v>
+      </c>
+      <c r="H33" t="str">
+        <v>רחוב הדקל 32</v>
+      </c>
+      <c r="I33" t="str">
+        <v>מודיעין עילית</v>
+      </c>
+      <c r="J33" t="str">
+        <v>02-513232</v>
+      </c>
+      <c r="K33" t="str">
+        <v>050-71032</v>
+      </c>
+      <c r="L33" t="str">
+        <v>052-81032</v>
+      </c>
+      <c r="M33" t="str">
+        <v>058-91032</v>
+      </c>
+      <c r="N33" t="str">
+        <v>נתיבות</v>
+      </c>
+      <c r="O33" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P33" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q33" t="str">
         <v>ללא הוראה</v>
       </c>
-      <c r="G33" t="str">
+      <c r="R33" t="str">
         <v>חינוך מיוחד</v>
       </c>
-      <c r="H33" t="str">
-        <v/>
-      </c>
-      <c r="I33" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J33" t="str">
+      <c r="S33" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T33" t="str">
+        <v/>
+      </c>
+      <c r="U33">
+        <v>6</v>
+      </c>
+      <c r="V33" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>תמר לוי</v>
+        <v/>
       </c>
       <c r="B34" t="str">
+        <v>חנה</v>
+      </c>
+      <c r="C34" t="str">
+        <v>לוי</v>
+      </c>
+      <c r="D34" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E34" t="str">
         <v>200000033</v>
       </c>
-      <c r="C34">
-        <v>6</v>
-      </c>
-      <c r="D34" t="str">
-        <v>א</v>
-      </c>
-      <c r="E34" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F34" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G34" t="str">
+        <v>2004-09-06</v>
+      </c>
+      <c r="H34" t="str">
+        <v>רחוב הדקל 33</v>
+      </c>
+      <c r="I34" t="str">
+        <v>ביתר עילית</v>
+      </c>
+      <c r="J34" t="str">
+        <v>02-513333</v>
+      </c>
+      <c r="K34" t="str">
+        <v>050-71033</v>
+      </c>
+      <c r="L34" t="str">
+        <v>052-81033</v>
+      </c>
+      <c r="M34" t="str">
+        <v>058-91033</v>
+      </c>
+      <c r="N34" t="str">
+        <v>בית יעקב</v>
+      </c>
+      <c r="O34" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P34" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q34" t="str">
         <v>הוראה</v>
       </c>
-      <c r="G34" t="str">
+      <c r="R34" t="str">
         <v>חשבונאות</v>
       </c>
-      <c r="H34" t="str">
+      <c r="S34" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T34" t="str">
         <v>תכנות</v>
       </c>
-      <c r="I34" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J34" t="str">
+      <c r="U34">
+        <v>6</v>
+      </c>
+      <c r="V34" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>נעמי לוי</v>
+        <v/>
       </c>
       <c r="B35" t="str">
+        <v>רבקה</v>
+      </c>
+      <c r="C35" t="str">
+        <v>לוי</v>
+      </c>
+      <c r="D35" t="str">
+        <v>יג 2</v>
+      </c>
+      <c r="E35" t="str">
         <v>200000034</v>
       </c>
-      <c r="C35">
-        <v>6</v>
-      </c>
-      <c r="D35" t="str">
-        <v>א</v>
-      </c>
-      <c r="E35" t="str">
-        <v>יג 2</v>
-      </c>
       <c r="F35" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G35" t="str">
+        <v>2005-10-07</v>
+      </c>
+      <c r="H35" t="str">
+        <v>רחוב הדקל 34</v>
+      </c>
+      <c r="I35" t="str">
+        <v>אלעד</v>
+      </c>
+      <c r="J35" t="str">
+        <v>02-513434</v>
+      </c>
+      <c r="K35" t="str">
+        <v>050-71034</v>
+      </c>
+      <c r="L35" t="str">
+        <v>052-81034</v>
+      </c>
+      <c r="M35" t="str">
+        <v>058-91034</v>
+      </c>
+      <c r="N35" t="str">
+        <v>הסמינר העירוני</v>
+      </c>
+      <c r="O35" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P35" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q35" t="str">
         <v>הוראה מקוצרת</v>
       </c>
-      <c r="G35" t="str">
+      <c r="R35" t="str">
         <v>תכנות</v>
       </c>
-      <c r="H35" t="str">
-        <v/>
-      </c>
-      <c r="I35" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J35" t="str">
+      <c r="S35" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T35" t="str">
+        <v/>
+      </c>
+      <c r="U35">
+        <v>6</v>
+      </c>
+      <c r="V35" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ברכה לוי</v>
+        <v/>
       </c>
       <c r="B36" t="str">
+        <v>לאה</v>
+      </c>
+      <c r="C36" t="str">
+        <v>לוי</v>
+      </c>
+      <c r="D36" t="str">
+        <v>יג 1</v>
+      </c>
+      <c r="E36" t="str">
         <v>200000035</v>
       </c>
-      <c r="C36">
-        <v>6</v>
-      </c>
-      <c r="D36" t="str">
-        <v>א</v>
-      </c>
-      <c r="E36" t="str">
-        <v>יג 1</v>
-      </c>
       <c r="F36" t="str">
+        <v>ט״ו בשבט תשס״ה</v>
+      </c>
+      <c r="G36" t="str">
+        <v>2006-11-08</v>
+      </c>
+      <c r="H36" t="str">
+        <v>רחוב הדקל 35</v>
+      </c>
+      <c r="I36" t="str">
+        <v>חיפה</v>
+      </c>
+      <c r="J36" t="str">
+        <v>02-513535</v>
+      </c>
+      <c r="K36" t="str">
+        <v>050-71035</v>
+      </c>
+      <c r="L36" t="str">
+        <v>052-81035</v>
+      </c>
+      <c r="M36" t="str">
+        <v>058-91035</v>
+      </c>
+      <c r="N36" t="str">
+        <v>אופקים</v>
+      </c>
+      <c r="O36" t="str">
+        <v>לא</v>
+      </c>
+      <c r="P36" t="str">
+        <v>א</v>
+      </c>
+      <c r="Q36" t="str">
         <v>הוראת מדעי המחשב</v>
       </c>
-      <c r="G36" t="str">
+      <c r="R36" t="str">
         <v>תנך</v>
       </c>
-      <c r="H36" t="str">
-        <v/>
-      </c>
-      <c r="I36" t="str">
-        <v>לא</v>
-      </c>
-      <c r="J36" t="str">
+      <c r="S36" t="str">
+        <v>לא</v>
+      </c>
+      <c r="T36" t="str">
+        <v/>
+      </c>
+      <c r="U36">
+        <v>6</v>
+      </c>
+      <c r="V36" t="str">
         <v>2027-09-01</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J36"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V36"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>קובץ 2: 35 תלמידות חדשות לשכבה א</v>
+        <v>קובץ 2: 35 תלמידות חדשות לשכבה א (אחרי קידום)</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חובה למלא את כל העמודות מלבד התמחות נוספת.</v>
+        <v>חובה: שם פרטי, משפחה, מ.ז., כיתה, מסלול, התמחות. שכבה מומלצת.</v>
       </c>
     </row>
     <row r="3">
@@ -1610,12 +2918,17 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אחרי קידום שנה — העלי רק את הקובץ הזה. הת.ז. לא חופפות לקובץ 1.</v>
+        <v>תוכנית חץ / פסיכולוגיה: כן או לא.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אחרי קידום שנה — העלי רק את הקובץ הזה לשכבה א. הת.ז. לא חופפות לקובץ 1.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
   </ignoredErrors>
 </worksheet>
 </file>